--- a/光伏配储项目/电价数据/2026/丹霞站.xlsx
+++ b/光伏配储项目/电价数据/2026/丹霞站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51258</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7756000000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6040599999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58447</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51455</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.53376</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.86786</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.43683</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.42522</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44292</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.03784000000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04014</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.03722</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03344</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.03543</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.04618</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.02277</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02555</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02465</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04901</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01776</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01285</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.02706</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01785</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.03963000000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04706</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03773</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.007730000000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20034</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.55644</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.67833</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5689299999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56604</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79887</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.62721</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63162</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7390099999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9298200000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65963</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58329</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.72339</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47283</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62393</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6037100000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.50062</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69179</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.99762</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.63649</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.54496</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6656299999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49341</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5049399999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48421</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55143</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45151</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26853</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24687</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.18963</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.17471</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.11022</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19591</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23539</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01547</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.16543</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.03989</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.03003</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.00154</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.13689</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.19803</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.18489</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.02252</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04201</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.03583</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.43836</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.5863200000000001</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.48428</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.58782</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.53285</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67157</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63205</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7194400000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76578</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47157</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.46238</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44227</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50985</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42934</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44524</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25306</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20907</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27191</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.44398</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.47403</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.5091100000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45849</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46312</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45199</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.52579</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52565</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6089</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.57759</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59609</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46391</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42263</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48226</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41987</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12473</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24128</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20133</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56021</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21599</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.22882</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16977</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.10985</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.0212</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.03569</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.23921</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.01691</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02581</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.10211</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19398</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19435</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10222</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.10148</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.10226</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16447</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31617</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.21545</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.2244</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.21625</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.21042</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04474</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.22123</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21728</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.19528</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02874</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09676999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03213000000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0329</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03501</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03721</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03425</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04082</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03823</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.03687</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05796</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.01087</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03407</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09597</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35075</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65349</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01242</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21081</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05155</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19973</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33528</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31698</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9140900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86252</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29603</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8871599999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18675</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86848</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5356599999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3305</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03267</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53044</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79069</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5295299999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7726799999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7773099999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87674</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87371</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49287</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39953</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20664</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6215000000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53823</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49759</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43708</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58536</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5955499999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60112</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58011</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8596200000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.79279</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8040700000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.54753</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45156</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91799</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46442</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46352</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49897</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16624</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19286</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.11236</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44275</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59493</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88962</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45673</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16042</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69977</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79059</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66415</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5787899999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44954</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43431</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43444</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43373</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49454</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55069</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15693</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00945</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25526</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56975</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46194</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.84629</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46417</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43617</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32327</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14163</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15283</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.00396</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13618</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24734</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13672</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.18746</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.05373</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.00296</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.01439</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10787</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10743</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12644</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13586</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14075</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43836</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44261</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34814</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53688</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46741</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42266</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.18521</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.16952</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.05596</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20078</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18492</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24331</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.05975</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25964</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35982</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.47581</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.52776</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24943</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.47658</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40613</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6898500000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50989</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22209</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3156</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.19202</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.22356</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.18463</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.21877</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.24405</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.24478</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34947</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.22134</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.09601999999999999</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.08951000000000001</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.09287000000000001</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.09676999999999999</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.07206</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.06909</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.11343</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.09468</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.09387999999999999</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.09558</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.04144</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.09542</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.09831000000000001</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.09506000000000001</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.09806999999999999</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.22093</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65638</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7696000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45734</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3442</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14848</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.07926000000000001</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.07959000000000001</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19988</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.06998</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21644</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.23109</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43222</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6393099999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59693</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6045499999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48457</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8094600000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48717</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.81163</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44158</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48897</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47013</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42979</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3598</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48841</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48212</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41569</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41634</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.11869</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44672</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.19362</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.08506</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.10149</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.11225</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.13116</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.07886</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.23169</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.23794</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.10538</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.01935</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.06117</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.06126</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.10286</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.04493</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.13934</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.02826</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.04779</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.03747</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.04311</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.03356</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.06639</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.03017</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.03965999999999999</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.25224</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.25428</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49181</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5044</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5420900000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.68968</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.71084</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.91895</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5246499999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80589</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58216</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5248700000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83113</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77015</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234400000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67216</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47163</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47604</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46881</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5510499999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45384</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.27226</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.24988</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.10001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.04578</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.1251</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19754</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.12036</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.07926999999999999</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04518</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.06492000000000001</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.05385</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.05383</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.08885999999999999</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.07562999999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.10094</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.07709999999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.05585</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.05348</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01256</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.09125</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.08943999999999999</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.11908</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.10676</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.25825</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.25886</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36502</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44369</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22561</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22988</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23716</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24922</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.23113</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13935</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.26226</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.23947</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.24236</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.06511</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.23671</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16939</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18751</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.24291</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23384</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23951</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.21665</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.04996</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2106</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.21906</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.19923</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.23834</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.24325</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.20293</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.24669</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34107</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22755</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.22544</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25513</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28447</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.1238</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.26125</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.76436</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75459</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.58177</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02555</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22706</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17921</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.20222</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.20138</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17646</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.06367</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.04794</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.09834999999999999</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.00899</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.03183</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04145</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.01312</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0406</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.21019</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.2099</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01613</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18183</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.19387</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18889</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16231</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25653</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.28569</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32151</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.16799</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.51979</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.22539</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.11335</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.06924</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.14249</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.09514</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14175</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.25375</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.22226</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.23925</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.24972</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.24815</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33997</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.82045</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5360199999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42558</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.24664</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.25401</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.22813</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.08693000000000001</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.10836</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.25302</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.10701</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.22367</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.22362</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.22437</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.10635</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.10039</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.10769</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.10664</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.10841</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.09892000000000001</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.21834</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.11593</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.47093</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.41884</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.45402</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33777</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.22143</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.11523</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.26232</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.22194</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44715</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.09462000000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.22988</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.08735</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.12117</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.11609</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.11645</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.21878</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.25036</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.09887</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.09049</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.10575</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.11048</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.09668</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.22993</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.25706</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.11765</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.23494</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.13111</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.42442</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.42172</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.46279</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7445499999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.42618</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34417</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.23661</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.24608</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.09851</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.24417</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.24351</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.24982</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.25271</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24378</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.26153</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.09197</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.10753</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.24466</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.22756</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.04529</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.08456999999999999</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21613</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.009390000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.24558</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.06688</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.06388000000000001</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.03504</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01868</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.04265</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03296</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08739</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02052</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.05922</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.05007</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.10655</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.10978</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.11396</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.11025</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.26629</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.26705</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.12347</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.13158</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.22794</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25078</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.25753</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.25621</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.24878</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.21268</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.24947</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.24704</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.5824900000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.46005</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.24948</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.24594</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.25248</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.24331</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.24615</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.11236</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.06856999999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.10714</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.10328</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.2244</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.05837</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.13192</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07121</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.12517</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.06819</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.01945</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.09909</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.00291</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.03816</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.01517</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.13802</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.01771</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.01245</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49802</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.26493</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.49435</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.25593</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33524</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.09991</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.24799</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.22153</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.24571</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.08392000000000001</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22622</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.06034</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.02903</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.25079</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23622</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13727</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.03639</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04254</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.02457</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.02357</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.0255</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.03481</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.10723</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.17003</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.03075</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.01373</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.00942</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.04234</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.03691</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.03655</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.00021</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.01199</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.25156</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.22935</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.24332</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.24779</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.24656</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.24675</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25832</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47465</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37731</v>
       </c>
     </row>
   </sheetData>
